--- a/examples/Newberry/3D/config/newberry_superhot_config.xlsx
+++ b/examples/Newberry/3D/config/newberry_superhot_config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10703"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smello\code\geoPFA\examples\Newberry\3D\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ntaverna/Documents/geoPFA General/geoPFA workshop/geoPFA/examples/Newberry/3D/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F8CB64D-5A57-40CA-8EEC-F00E6774D873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0004B8-831E-0C48-9D80-9A7B84F6C2BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2715" yWindow="-14940" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
   <si>
     <t>criteria</t>
   </si>
@@ -275,9 +275,6 @@
   </si>
   <si>
     <t>Magnitude</t>
-  </si>
-  <si>
-    <t>epsg:26910</t>
   </si>
   <si>
     <t>reservoir</t>
@@ -651,14 +648,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="16" max="16" width="8.88671875" customWidth="1"/>
+    <col min="16" max="16" width="8.83203125" customWidth="1"/>
     <col min="17" max="17" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -711,7 +708,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>61</v>
       </c>
@@ -746,13 +743,13 @@
         <v>67</v>
       </c>
       <c r="L2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M2">
         <v>26910</v>
       </c>
       <c r="N2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O2" t="s">
         <v>68</v>
@@ -761,7 +758,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="F3" t="s">
         <v>70</v>
       </c>
@@ -781,13 +778,13 @@
         <v>67</v>
       </c>
       <c r="L3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M3">
         <v>26910</v>
       </c>
       <c r="N3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O3" t="s">
         <v>68</v>
@@ -796,7 +793,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="F4" t="s">
         <v>73</v>
       </c>
@@ -822,7 +819,7 @@
         <v>26910</v>
       </c>
       <c r="N4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="O4" t="s">
         <v>79</v>
@@ -831,7 +828,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="F5" t="s">
         <v>80</v>
       </c>
@@ -857,18 +854,18 @@
         <v>26910</v>
       </c>
       <c r="N5" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="O5" t="s">
         <v>68</v>
       </c>
       <c r="P5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D6">
         <v>0.4</v>
@@ -895,22 +892,22 @@
         <v>67</v>
       </c>
       <c r="L6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M6">
         <v>26910</v>
       </c>
       <c r="N6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="F7" t="s">
         <v>70</v>
       </c>
@@ -930,22 +927,22 @@
         <v>67</v>
       </c>
       <c r="L7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M7">
         <v>26910</v>
       </c>
       <c r="N7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P7" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="F8" t="s">
         <v>80</v>
       </c>
@@ -971,18 +968,18 @@
         <v>26910</v>
       </c>
       <c r="N8" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="O8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="F9" t="s">
         <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="F9" t="s">
-        <v>91</v>
       </c>
       <c r="G9">
         <v>0.249</v>
@@ -1006,18 +1003,18 @@
         <v>26910</v>
       </c>
       <c r="N9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="O9" t="s">
         <v>68</v>
       </c>
       <c r="P9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="F10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G10">
         <v>0.249</v>
@@ -1044,12 +1041,12 @@
         <v>68</v>
       </c>
       <c r="P10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D11">
         <v>0.2</v>
@@ -1076,22 +1073,22 @@
         <v>67</v>
       </c>
       <c r="L11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M11">
         <v>26910</v>
       </c>
       <c r="N11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="F12" t="s">
         <v>70</v>
       </c>
@@ -1111,13 +1108,13 @@
         <v>67</v>
       </c>
       <c r="L12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M12">
         <v>26910</v>
       </c>
       <c r="N12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O12" t="s">
         <v>68</v>
@@ -1126,7 +1123,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="F13" t="s">
         <v>80</v>
       </c>
@@ -1152,16 +1149,16 @@
         <v>26910</v>
       </c>
       <c r="N13" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="O13" t="s">
         <v>68</v>
       </c>
       <c r="P13" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="F14" t="s">
         <v>73</v>
       </c>
@@ -1187,7 +1184,7 @@
         <v>26910</v>
       </c>
       <c r="N14" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="O14" t="s">
         <v>68</v>
@@ -1204,15 +1201,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36350C53-10DF-40B8-A514-0EA653A43886}">
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.109375" customWidth="1"/>
-    <col min="2" max="2" width="37.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.44140625" customWidth="1"/>
-    <col min="4" max="4" width="72.44140625" customWidth="1"/>
+    <col min="1" max="1" width="24.1640625" customWidth="1"/>
+    <col min="2" max="2" width="37.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5" customWidth="1"/>
+    <col min="4" max="4" width="72.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>17</v>
       </c>
@@ -1226,7 +1223,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1240,7 +1237,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1254,7 +1251,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1268,7 +1265,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -1282,7 +1279,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
@@ -1296,7 +1293,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
@@ -1310,7 +1307,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
@@ -1324,7 +1321,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="58.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>14</v>
       </c>
@@ -1338,7 +1335,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>15</v>
       </c>
@@ -1352,7 +1349,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>7</v>
       </c>
@@ -1366,7 +1363,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="48" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1380,7 +1377,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="48" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
@@ -1394,7 +1391,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>25</v>
       </c>
@@ -1408,7 +1405,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>11</v>
       </c>
@@ -1422,7 +1419,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>13</v>
       </c>
@@ -1436,7 +1433,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
@@ -1450,13 +1447,13 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
